--- a/data/trans_dic/IP1021_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen dolor crónico</t>
+          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,86</t>
+          <t>0,33; 2,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,95</t>
+          <t>0,67; 3,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,53</t>
+          <t>0,65; 2,68</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,98</t>
+          <t>1,34; 6,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,86</t>
+          <t>0,73; 5,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,46</t>
+          <t>1,54; 4,5</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,16</t>
+          <t>1,07; 4,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,93</t>
+          <t>0,57; 3,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,26</t>
+          <t>1,04; 3,14</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,06</t>
+          <t>1,27; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,83</t>
+          <t>0,93; 2,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,49</t>
+          <t>1,28; 2,5</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3075</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4783</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>520; 4540</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1228; 7236</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2208; 9150</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4767</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9977</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2316; 10411</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1548; 10915</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5941; 17335</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6166</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4901</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11067</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2946; 11295</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1731; 10878</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6042; 18259</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>13084</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12743</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25827</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>8460; 20236</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7113; 21086</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18255; 35664</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1021_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Edad-trans_dic.xlsx
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,85</t>
+          <t>0,25; 2,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,96</t>
+          <t>0,58; 3,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,68</t>
+          <t>0,65; 2,58</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,02</t>
+          <t>1,44; 6,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,15</t>
+          <t>0,91; 5,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,5</t>
+          <t>1,53; 4,6</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,1</t>
+          <t>1,09; 3,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,56</t>
+          <t>0,57; 3,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,14</t>
+          <t>1,06; 3,19</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,04</t>
+          <t>1,28; 2,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,77</t>
+          <t>0,96; 2,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,5</t>
+          <t>1,23; 2,51</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>520; 4540</t>
+          <t>398; 4134</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1228; 7236</t>
+          <t>1064; 6880</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2208; 9150</t>
+          <t>2224; 8807</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2316; 10411</t>
+          <t>2493; 10501</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1548; 10915</t>
+          <t>1926; 11238</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5941; 17335</t>
+          <t>5898; 17709</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2946; 11295</t>
+          <t>3013; 10974</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1731; 10878</t>
+          <t>1750; 11198</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6042; 18259</t>
+          <t>6156; 18536</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8460; 20236</t>
+          <t>8534; 19397</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7113; 21086</t>
+          <t>7345; 20776</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18255; 35664</t>
+          <t>17531; 35836</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1021_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,6</t>
+          <t>0,46; 3,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,77</t>
+          <t>0,24; 2,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,58</t>
+          <t>0,6; 2,22</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,07</t>
+          <t>0,81; 4,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,3</t>
+          <t>1,35; 6,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,6</t>
+          <t>1,43; 4,41</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,98</t>
+          <t>0,62; 3,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,67</t>
+          <t>1,29; 4,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,19</t>
+          <t>1,15; 3,38</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,92</t>
+          <t>0,95; 2,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,73</t>
+          <t>1,34; 3,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,51</t>
+          <t>1,29; 2,54</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>3778</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>398; 4134</t>
+          <t>726; 5293</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1064; 6880</t>
+          <t>349; 3969</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2224; 8807</t>
+          <t>1820; 6723</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9628</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2493; 10501</t>
+          <t>1611; 9044</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1926; 11238</t>
+          <t>2359; 10621</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5898; 17709</t>
+          <t>5366; 16500</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>11094</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3013; 10974</t>
+          <t>1806; 11289</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1750; 11198</t>
+          <t>3297; 11700</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6156; 18536</t>
+          <t>6321; 18554</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>24500</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8534; 19397</t>
+          <t>6666; 19304</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7345; 20776</t>
+          <t>8451; 20185</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17531; 35836</t>
+          <t>17123; 33763</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1021_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 3,36</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,24; 2,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 2,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,81; 4,53</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 6,08</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 4,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 3,86</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 4,56</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 3,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,95; 2,76</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,34; 3,21</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 2,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,70 +552,40 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -952,69 +595,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.0144402921793065</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01032798747178479</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01246558689701111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3778</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.004609347291231938</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.002397529321480099</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.006005462373002248</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>726; 5293</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>349; 3969</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1820; 6723</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.03360469776569738</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.02727819435851116</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.02218573671609888</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +650,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.02125123244706577</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.03084251882700987</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.02572783498952469</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5387</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9628</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.008070139075507703</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.01350790653481124</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.01433716896965511</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1611; 9044</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2359; 10621</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5366; 16500</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.04531884139844522</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.06080543191711259</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.04408998192629811</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +705,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01622347299252424</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.0247358121362893</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.02019994231745253</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6346</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11094</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.006171118783632108</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.01285164918423556</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.01150868883939785</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>1806; 11289</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3297; 11700</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>6321; 18554</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.0385762009573004</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.04560404671737431</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.03378440695414781</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +760,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.01608439139545351</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.02104898416082531</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.01843326270963022</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>11263</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>13236</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24500</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.009519442113418772</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.01343866702896428</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.01288276935184691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>6666; 19304</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>8451; 20185</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17123; 33763</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.02756616270834144</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.03209938588483536</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.02540270349315675</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +825,437 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2275</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1503</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>3778</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>726</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>349</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5293</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>3969</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>6723</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4241</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5387</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>9628</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1611</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2359</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>5366</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>9044</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>10621</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>4748</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>6346</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>11094</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1806</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3297</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>6321</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>11289</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>11700</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>18554</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>11263</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>13236</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>6666</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>8451</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>17123</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>19304</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>20185</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>33763</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>